--- a/SF.xlsx
+++ b/SF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fnsul-my.sharepoint.com/personal/jungbin_lee_fnsusa_com/Documents/바탕 화면/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE127A32-8D79-4C40-9169-577A9172BCD0}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{476E4662-48CD-49F0-BAB6-DE202E71846C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE368B0D-5E19-4AE2-AF1A-E02F0281253F}"/>
   </bookViews>
@@ -320,6 +320,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -654,6 +658,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2633</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -692,7 +699,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2580</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -700,7 +707,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2578</v>
+        <v>904</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -769,7 +776,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2575</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -806,7 +813,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2565</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -830,7 +837,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2150</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -838,7 +845,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>2527</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -878,7 +885,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>2615</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -886,7 +893,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>2613</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -902,18 +909,24 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>2440</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>34</v>
       </c>
+      <c r="B35">
+        <v>2637</v>
+      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>35</v>
       </c>
+      <c r="B36">
+        <v>2607</v>
+      </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -927,9 +940,6 @@
       <c r="A38" t="s">
         <v>37</v>
       </c>
-      <c r="B38">
-        <v>2206</v>
-      </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -944,7 +954,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>2566</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -960,7 +970,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>2602</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -968,7 +978,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>2608</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -976,34 +986,34 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>2630</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>44</v>
       </c>
-      <c r="B45">
-        <v>2582</v>
-      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>45</v>
       </c>
-      <c r="B46">
-        <v>2571</v>
-      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>46</v>
       </c>
+      <c r="B47">
+        <v>2609</v>
+      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>47</v>
       </c>
+      <c r="B48">
+        <v>2648</v>
+      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -1114,9 +1124,6 @@
       <c r="A64" t="s">
         <v>63</v>
       </c>
-      <c r="B64">
-        <v>2484</v>
-      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -1151,9 +1158,6 @@
       <c r="A69" t="s">
         <v>75</v>
       </c>
-      <c r="B69">
-        <v>2581</v>
-      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -1162,6 +1166,9 @@
       <c r="B70">
         <v>2209</v>
       </c>
+      <c r="C70">
+        <v>2581</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -1179,10 +1186,10 @@
         <v>69</v>
       </c>
       <c r="B72">
-        <v>2594</v>
+        <v>2612</v>
       </c>
       <c r="C72">
-        <v>2580</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1190,7 +1197,7 @@
         <v>70</v>
       </c>
       <c r="B73">
-        <v>2552</v>
+        <v>2626</v>
       </c>
       <c r="C73">
         <v>221</v>
@@ -1201,15 +1208,18 @@
         <v>71</v>
       </c>
       <c r="B74">
+        <v>2568</v>
+      </c>
+      <c r="C74">
         <v>2208</v>
-      </c>
-      <c r="C74">
-        <v>2568</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>72</v>
+      </c>
+      <c r="B75">
+        <v>2632</v>
       </c>
       <c r="C75">
         <v>651</v>

--- a/SF.xlsx
+++ b/SF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fnsul-my.sharepoint.com/personal/jungbin_lee_fnsusa_com/Documents/바탕 화면/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{476E4662-48CD-49F0-BAB6-DE202E71846C}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C95B294-F1DF-49BC-846E-8213F9A10FC4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE368B0D-5E19-4AE2-AF1A-E02F0281253F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>SF1</t>
   </si>
@@ -267,6 +267,18 @@
   </si>
   <si>
     <t>SFE-2</t>
+  </si>
+  <si>
+    <t>51203_1N</t>
+  </si>
+  <si>
+    <t>31006_1G</t>
+  </si>
+  <si>
+    <t>81002_1K</t>
+  </si>
+  <si>
+    <t>31004_1G</t>
   </si>
 </sst>
 </file>
@@ -658,9 +670,6 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2633</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -675,7 +684,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2628</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -683,32 +692,23 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2586</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>2624</v>
-      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>2572</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>904</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -722,8 +722,8 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>2629</v>
+      <c r="B10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -746,24 +746,18 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>2125</v>
-      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>2091</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>2605</v>
+      <c r="B15" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -775,9 +769,6 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>2650</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -788,16 +779,13 @@
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>2516</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2478</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -805,7 +793,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>906</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -813,7 +801,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2613</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -821,16 +809,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2569</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24">
-        <v>2570</v>
-      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -844,8 +829,8 @@
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26">
-        <v>2582</v>
+      <c r="B26" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -853,16 +838,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>908</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28">
-        <v>926</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -877,7 +859,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>2610</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -885,16 +867,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>2579</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32">
-        <v>2333</v>
-      </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -908,32 +887,26 @@
       <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34">
-        <v>2635</v>
-      </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>2637</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>35</v>
       </c>
-      <c r="B36">
-        <v>2607</v>
-      </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>36</v>
       </c>
       <c r="B37">
-        <v>2596</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -953,16 +926,13 @@
       <c r="A40" t="s">
         <v>39</v>
       </c>
-      <c r="B40">
-        <v>2484</v>
-      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>40</v>
       </c>
       <c r="B41">
-        <v>2588</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -970,7 +940,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>2576</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -978,7 +948,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>2584</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -986,7 +956,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>2636</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -1004,7 +974,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>2609</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -1012,7 +982,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>2648</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1020,7 +990,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>2135</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1028,7 +998,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>2174</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1049,7 +1019,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>1129</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -1062,7 +1032,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>2232</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1074,8 +1044,8 @@
       <c r="A57" t="s">
         <v>56</v>
       </c>
-      <c r="B57">
-        <v>2105</v>
+      <c r="B57" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1088,7 +1058,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>2158</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1109,7 +1079,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>2161</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -1117,20 +1087,23 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>2410</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>63</v>
       </c>
+      <c r="B64">
+        <v>2712</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>64</v>
       </c>
       <c r="B65">
-        <v>2614</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -1138,21 +1111,21 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>2601</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>66</v>
       </c>
+      <c r="B67">
+        <v>2449</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>74</v>
       </c>
-      <c r="B68">
-        <v>2449</v>
-      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -1163,11 +1136,8 @@
       <c r="A70" t="s">
         <v>67</v>
       </c>
-      <c r="B70">
-        <v>2209</v>
-      </c>
       <c r="C70">
-        <v>2581</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1175,7 +1145,7 @@
         <v>68</v>
       </c>
       <c r="B71">
-        <v>1001</v>
+        <v>2727</v>
       </c>
       <c r="C71">
         <v>1717</v>
@@ -1186,10 +1156,10 @@
         <v>69</v>
       </c>
       <c r="B72">
-        <v>2612</v>
+        <v>2771</v>
       </c>
       <c r="C72">
-        <v>2480</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1197,7 +1167,7 @@
         <v>70</v>
       </c>
       <c r="B73">
-        <v>2626</v>
+        <v>2603</v>
       </c>
       <c r="C73">
         <v>221</v>
@@ -1208,7 +1178,7 @@
         <v>71</v>
       </c>
       <c r="B74">
-        <v>2568</v>
+        <v>2689</v>
       </c>
       <c r="C74">
         <v>2208</v>
@@ -1219,7 +1189,7 @@
         <v>72</v>
       </c>
       <c r="B75">
-        <v>2632</v>
+        <v>1147</v>
       </c>
       <c r="C75">
         <v>651</v>
@@ -1229,11 +1199,8 @@
       <c r="A76" t="s">
         <v>73</v>
       </c>
-      <c r="B76">
-        <v>1775</v>
-      </c>
       <c r="C76">
-        <v>2560</v>
+        <v>2711</v>
       </c>
     </row>
   </sheetData>

--- a/SF.xlsx
+++ b/SF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fnsul-my.sharepoint.com/personal/jungbin_lee_fnsusa_com/Documents/바탕 화면/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C95B294-F1DF-49BC-846E-8213F9A10FC4}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7347CEA2-56E6-4A10-BC1E-21D86F1D3B54}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE368B0D-5E19-4AE2-AF1A-E02F0281253F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
   <si>
     <t>SF1</t>
   </si>
@@ -275,10 +275,25 @@
     <t>31006_1G</t>
   </si>
   <si>
-    <t>81002_1K</t>
-  </si>
-  <si>
-    <t>31004_1G</t>
+    <t>location</t>
+  </si>
+  <si>
+    <t>QC</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>231004_1G</t>
+  </si>
+  <si>
+    <t>251001_1G</t>
+  </si>
+  <si>
+    <t>181002_1K</t>
+  </si>
+  <si>
+    <t>new</t>
   </si>
 </sst>
 </file>
@@ -655,428 +670,401 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8883645C-3432-47A1-B329-9577D994FDF6}">
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B2">
         <v>1547</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>2654</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>2717</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>2441</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>1937</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>2561</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>15</v>
+      <c r="B16" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>2703</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>363</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22">
-        <v>2333</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>2696</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>2647</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>2647</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>2478</v>
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>2757</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>2224</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>2747</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>2707</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>2796</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33">
-        <v>2375</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>2747</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35">
-        <v>2750</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37">
-        <v>2484</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>2774</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39">
-        <v>2524</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>2798</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41">
-        <v>2684</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42">
-        <v>2173</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43">
-        <v>2720</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44">
-        <v>2783</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>2794</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47">
-        <v>2718</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48">
-        <v>2640</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49">
-        <v>2743</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50">
-        <v>2749</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51">
-        <v>2032</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>2797</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53">
-        <v>2705</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>2775</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55">
-        <v>2710</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>2755</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59">
-        <v>2759</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>2333</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61">
-        <v>2438</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62">
         <v>2737</v>
@@ -1084,48 +1072,42 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63">
-        <v>2697</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64">
-        <v>2712</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>64</v>
-      </c>
-      <c r="B65">
-        <v>2768</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66">
-        <v>2766</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67">
-        <v>2449</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>74</v>
       </c>
+      <c r="B68">
+        <v>2792</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -1134,73 +1116,63 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>67</v>
-      </c>
-      <c r="C70">
-        <v>2724</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>68</v>
-      </c>
-      <c r="B71">
-        <v>2727</v>
-      </c>
-      <c r="C71">
-        <v>1717</v>
+        <v>67</v>
+      </c>
+      <c r="C71" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>69</v>
-      </c>
-      <c r="B72">
-        <v>2771</v>
+        <v>68</v>
       </c>
       <c r="C72">
-        <v>2765</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>70</v>
-      </c>
-      <c r="B73">
-        <v>2603</v>
-      </c>
-      <c r="C73">
-        <v>221</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="C74">
-        <v>2208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>72</v>
-      </c>
-      <c r="B75">
-        <v>1147</v>
+        <v>71</v>
       </c>
       <c r="C75">
-        <v>651</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>72</v>
+      </c>
+      <c r="C76">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>73</v>
       </c>
-      <c r="C76">
-        <v>2711</v>
+      <c r="C77">
+        <v>2799</v>
       </c>
     </row>
   </sheetData>
